--- a/Bank & RMC Details.xlsx
+++ b/Bank & RMC Details.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\neeth\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naveen\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAF5E4BD-4765-4EE8-8435-27799C956379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C79BFFB-1122-4C35-BCE9-53C1F7EA4304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2856" yWindow="2856" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bank Details" sheetId="5" r:id="rId1"/>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataChecksum="pDiCCZnowhlhG8vO0vsKg3EH0crR7lTVxioPa/IgRgI="/>
     </ext>
@@ -582,7 +585,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -652,9 +655,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -669,10 +672,9 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -896,24 +898,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L1000"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="26" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="26" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>141</v>
       </c>
@@ -951,7 +953,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -970,8 +972,14 @@
       <c r="F2" s="4">
         <v>2.2499999999999999E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="4"/>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1002,8 +1010,10 @@
       <c r="J3" s="4">
         <v>2.1899999999999999E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K3" s="3"/>
+      <c r="L3" s="4"/>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1041,7 +1051,7 @@
         <v>2.1499999999999998E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1079,8 +1089,8 @@
         <v>1.9900000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -1089,13 +1099,13 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="4">
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="4">
         <v>2.1899999999999999E-2</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -1110,15 +1120,15 @@
       <c r="J6" s="4">
         <v>1.89E-2</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="4">
         <v>1.7899999999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -1127,13 +1137,13 @@
       <c r="C7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="4">
         <v>2.5899999999999999E-2</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="4">
         <v>2.29E-2</v>
       </c>
       <c r="G7" s="3" t="s">
@@ -1148,15 +1158,15 @@
       <c r="J7" s="4">
         <v>1.9900000000000001E-2</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="4">
         <v>1.89E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6">
+    <row r="8" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -1165,13 +1175,13 @@
       <c r="C8" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="4">
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="4">
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="G8" s="3" t="s">
@@ -1186,15 +1196,15 @@
       <c r="J8" s="4">
         <v>2.0899999999999998E-2</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="4">
         <v>1.9900000000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="6">
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -1203,13 +1213,13 @@
       <c r="C9" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="4">
         <v>2.9899999999999999E-2</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="4">
         <v>2.69E-2</v>
       </c>
       <c r="G9" s="3" t="s">
@@ -1224,1004 +1234,1004 @@
       <c r="J9" s="4">
         <v>2.29E-2</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="4">
         <v>2.1899999999999999E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="241" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="242" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="243" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="244" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="245" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="246" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="247" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="248" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="249" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="250" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="251" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="252" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="253" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="254" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="255" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="256" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="257" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="258" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="259" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="260" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="261" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="262" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="263" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="264" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="266" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="267" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="268" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="269" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="270" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="271" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="272" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="273" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="274" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="275" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="276" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="277" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="278" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="279" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="280" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="281" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="282" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="283" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="284" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="285" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="286" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="287" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="288" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="324" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="325" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="326" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="327" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="328" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="329" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="330" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="331" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="332" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="333" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="334" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="335" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="336" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="337" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="338" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="339" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="340" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="341" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="342" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="343" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="344" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="345" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="346" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="347" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="348" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="349" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="350" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="351" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="352" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="353" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="354" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="355" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="356" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="357" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="358" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="359" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="360" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="361" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="362" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="363" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="364" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="365" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="366" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="367" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="368" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="369" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="370" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="371" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="372" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="373" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="374" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="375" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="376" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="377" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="378" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="379" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="380" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="381" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="382" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="383" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="384" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -2231,22 +2241,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H1000"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="27" width="8.5546875" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="27" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>171</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -2255,24 +2265,24 @@
       <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="12">
         <v>2025</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2281,28 +2291,28 @@
       <c r="D2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>4300*1.05</f>
         <v>4515</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="9">
         <f>5200*1.05</f>
         <v>5460</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="9">
         <f>5900*1.05</f>
         <v>6195</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="9">
         <f>9300*1.05</f>
         <v>9765</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="12">
         <v>2025</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -2311,28 +2321,28 @@
       <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="9">
         <f t="shared" ref="E3:E7" si="0">4300*1.05</f>
         <v>4515</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="9">
         <f t="shared" ref="F3:F7" si="1">5200*1.05</f>
         <v>5460</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <f t="shared" ref="G3:G7" si="2">5900*1.05</f>
         <v>6195</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="9">
         <f t="shared" ref="H3:H7" si="3">9300*1.05</f>
         <v>9765</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="12">
         <v>2025</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -2341,28 +2351,28 @@
       <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="9">
         <f t="shared" si="0"/>
         <v>4515</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="9">
         <f t="shared" si="1"/>
         <v>5460</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <f t="shared" si="2"/>
         <v>6195</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="9">
         <f t="shared" si="3"/>
         <v>9765</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="12">
         <v>2025</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -2371,28 +2381,28 @@
       <c r="D5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="9">
         <f t="shared" si="0"/>
         <v>4515</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="9">
         <f t="shared" si="1"/>
         <v>5460</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="9">
         <f t="shared" si="2"/>
         <v>6195</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="9">
         <f t="shared" si="3"/>
         <v>9765</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="12">
         <v>2025</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -2401,28 +2411,28 @@
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <f t="shared" si="0"/>
         <v>4515</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <f t="shared" si="1"/>
         <v>5460</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="9">
         <f t="shared" si="2"/>
         <v>6195</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="9">
         <f t="shared" si="3"/>
         <v>9765</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="12">
         <v>2025</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -2431,28 +2441,28 @@
       <c r="D7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="9">
         <f t="shared" si="0"/>
         <v>4515</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="9">
         <f t="shared" si="1"/>
         <v>5460</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="9">
         <f t="shared" si="2"/>
         <v>6195</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="9">
         <f t="shared" si="3"/>
         <v>9765</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="12">
         <v>2025</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -2461,28 +2471,28 @@
       <c r="D8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="9">
         <f>5000*1.05</f>
         <v>5250</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="9">
         <f>6000*1.05</f>
         <v>6300</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="9">
         <f>6700*1.05</f>
         <v>7035</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="9">
         <f>11000*1.05</f>
         <v>11550</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="12">
         <v>2025</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -2491,28 +2501,28 @@
       <c r="D9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="9">
         <f t="shared" ref="E9:E14" si="4">5000*1.05</f>
         <v>5250</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="9">
         <f t="shared" ref="F9:F14" si="5">6000*1.05</f>
         <v>6300</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="9">
         <f t="shared" ref="G9:G14" si="6">6700*1.05</f>
         <v>7035</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="9">
         <f t="shared" ref="H9:H14" si="7">11000*1.05</f>
         <v>11550</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="12">
         <v>2025</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -2521,28 +2531,28 @@
       <c r="D10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="9">
         <f t="shared" si="4"/>
         <v>5250</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="9">
         <f t="shared" si="5"/>
         <v>6300</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="9">
         <f t="shared" si="6"/>
         <v>7035</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="9">
         <f t="shared" si="7"/>
         <v>11550</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="12">
         <v>2025</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -2551,28 +2561,28 @@
       <c r="D11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="9">
         <f t="shared" si="4"/>
         <v>5250</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="9">
         <f t="shared" si="5"/>
         <v>6300</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="9">
         <f t="shared" si="6"/>
         <v>7035</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="9">
         <f t="shared" si="7"/>
         <v>11550</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="12">
         <v>2025</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -2581,28 +2591,28 @@
       <c r="D12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="9">
         <f t="shared" si="4"/>
         <v>5250</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="9">
         <f t="shared" si="5"/>
         <v>6300</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="9">
         <f t="shared" si="6"/>
         <v>7035</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="9">
         <f t="shared" si="7"/>
         <v>11550</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="12">
         <v>2025</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -2611,28 +2621,28 @@
       <c r="D13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="9">
         <f t="shared" si="4"/>
         <v>5250</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="9">
         <f t="shared" si="5"/>
         <v>6300</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="9">
         <f t="shared" si="6"/>
         <v>7035</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="9">
         <f t="shared" si="7"/>
         <v>11550</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="12">
         <v>2025</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -2641,28 +2651,28 @@
       <c r="D14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <f t="shared" si="4"/>
         <v>5250</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="9">
         <f t="shared" si="5"/>
         <v>6300</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="9">
         <f t="shared" si="6"/>
         <v>7035</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="9">
         <f t="shared" si="7"/>
         <v>11550</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="12">
         <v>2025</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -2671,28 +2681,28 @@
       <c r="D15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="9">
         <f>4500*1.05</f>
         <v>4725</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="9">
         <f>5400*1.05</f>
         <v>5670</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="9">
         <f>6100*1.05</f>
         <v>6405</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="9">
         <f>9700*1.05</f>
         <v>10185</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="12">
         <v>2025</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -2701,28 +2711,28 @@
       <c r="D16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="9">
         <f t="shared" ref="E16:E19" si="8">4500*1.05</f>
         <v>4725</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="9">
         <f t="shared" ref="F16:F19" si="9">5400*1.05</f>
         <v>5670</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="9">
         <f t="shared" ref="G16:G19" si="10">6100*1.05</f>
         <v>6405</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="9">
         <f t="shared" ref="H16:H19" si="11">9700*1.05</f>
         <v>10185</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="12">
         <v>2025</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -2731,28 +2741,28 @@
       <c r="D17" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="9">
         <f t="shared" si="8"/>
         <v>4725</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="9">
         <f t="shared" si="9"/>
         <v>5670</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="9">
         <f t="shared" si="10"/>
         <v>6405</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="9">
         <f t="shared" si="11"/>
         <v>10185</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="12">
         <v>2025</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -2761,28 +2771,28 @@
       <c r="D18" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="9">
         <f t="shared" si="8"/>
         <v>4725</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="9">
         <f t="shared" si="9"/>
         <v>5670</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="9">
         <f t="shared" si="10"/>
         <v>6405</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="9">
         <f t="shared" si="11"/>
         <v>10185</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="12">
         <v>2025</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -2791,28 +2801,28 @@
       <c r="D19" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="9">
         <f t="shared" si="8"/>
         <v>4725</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="9">
         <f t="shared" si="9"/>
         <v>5670</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="9">
         <f t="shared" si="10"/>
         <v>6405</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="9">
         <f t="shared" si="11"/>
         <v>10185</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="12">
         <v>2025</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -2821,28 +2831,28 @@
       <c r="D20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="9">
         <f>4900*1.05</f>
         <v>5145</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="9">
         <f>5700*1.05</f>
         <v>5985</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="9">
         <f>6400*1.05</f>
         <v>6720</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="9">
         <f>10400*1.05</f>
         <v>10920</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="12">
         <v>2025</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -2851,28 +2861,28 @@
       <c r="D21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="9">
         <f t="shared" ref="E21:E29" si="12">4900*1.05</f>
         <v>5145</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="9">
         <f t="shared" ref="F21:F23" si="13">5700*1.05</f>
         <v>5985</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="9">
         <f t="shared" ref="G21:G23" si="14">6400*1.05</f>
         <v>6720</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="9">
         <f t="shared" ref="H21:H23" si="15">10400*1.05</f>
         <v>10920</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="12">
         <v>2025</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -2881,28 +2891,28 @@
       <c r="D22" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="9">
         <f t="shared" si="12"/>
         <v>5145</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="9">
         <f t="shared" si="13"/>
         <v>5985</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="9">
         <f t="shared" si="14"/>
         <v>6720</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="9">
         <f t="shared" si="15"/>
         <v>10920</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="12">
         <v>2025</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -2911,28 +2921,28 @@
       <c r="D23" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="9">
         <f t="shared" si="12"/>
         <v>5145</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="9">
         <f t="shared" si="13"/>
         <v>5985</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="9">
         <f t="shared" si="14"/>
         <v>6720</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="9">
         <f t="shared" si="15"/>
         <v>10920</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="12">
         <v>2025</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -2941,28 +2951,28 @@
       <c r="D24" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="9">
         <f t="shared" si="12"/>
         <v>5145</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="9">
         <f>5900*1.05</f>
         <v>6195</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="9">
         <f>6600*1.05</f>
         <v>6930</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="9">
         <f>10700*1.05</f>
         <v>11235</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="12">
         <v>2025</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -2971,28 +2981,28 @@
       <c r="D25" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="9">
         <f t="shared" si="12"/>
         <v>5145</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="9">
         <f t="shared" ref="F25:F29" si="16">5900*1.05</f>
         <v>6195</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="9">
         <f t="shared" ref="G25:G29" si="17">6600*1.05</f>
         <v>6930</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="9">
         <f t="shared" ref="H25:H29" si="18">10700*1.05</f>
         <v>11235</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="12">
         <v>2025</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -3001,28 +3011,28 @@
       <c r="D26" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="9">
         <f t="shared" si="12"/>
         <v>5145</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F26" s="9">
         <f t="shared" si="16"/>
         <v>6195</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="9">
         <f t="shared" si="17"/>
         <v>6930</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="9">
         <f t="shared" si="18"/>
         <v>11235</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="12">
         <v>2025</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -3031,28 +3041,28 @@
       <c r="D27" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="9">
         <f t="shared" si="12"/>
         <v>5145</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="9">
         <f t="shared" si="16"/>
         <v>6195</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="9">
         <f t="shared" si="17"/>
         <v>6930</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="9">
         <f t="shared" si="18"/>
         <v>11235</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="12">
         <v>2025</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -3061,28 +3071,28 @@
       <c r="D28" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="9">
         <f t="shared" si="12"/>
         <v>5145</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="9">
         <f t="shared" si="16"/>
         <v>6195</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="9">
         <f t="shared" si="17"/>
         <v>6930</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="9">
         <f t="shared" si="18"/>
         <v>11235</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B29" s="13">
+      <c r="B29" s="12">
         <v>2025</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -3091,28 +3101,28 @@
       <c r="D29" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="9">
         <f t="shared" si="12"/>
         <v>5145</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="9">
         <f t="shared" si="16"/>
         <v>6195</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="9">
         <f t="shared" si="17"/>
         <v>6930</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="9">
         <f t="shared" si="18"/>
         <v>11235</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B30" s="13">
+      <c r="B30" s="12">
         <v>2025</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -3121,28 +3131,28 @@
       <c r="D30" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="9">
         <f>3700*1.05</f>
         <v>3885</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="9">
         <f>4500*1.05</f>
         <v>4725</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="9">
         <f>5400*1.05</f>
         <v>5670</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="9">
         <f>8500*1.05</f>
         <v>8925</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="12">
         <v>2025</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -3151,28 +3161,28 @@
       <c r="D31" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="9">
         <f t="shared" ref="E31:E38" si="19">3700*1.05</f>
         <v>3885</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="9">
         <f t="shared" ref="F31:F38" si="20">4500*1.05</f>
         <v>4725</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="9">
         <f t="shared" ref="G31:G38" si="21">5400*1.05</f>
         <v>5670</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="9">
         <f t="shared" ref="H31:H38" si="22">8500*1.05</f>
         <v>8925</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="12">
         <v>2025</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -3181,28 +3191,28 @@
       <c r="D32" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E32" s="9">
         <f t="shared" si="19"/>
         <v>3885</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="9">
         <f t="shared" si="20"/>
         <v>4725</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="9">
         <f t="shared" si="21"/>
         <v>5670</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="9">
         <f t="shared" si="22"/>
         <v>8925</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B33" s="13">
+      <c r="B33" s="12">
         <v>2025</v>
       </c>
       <c r="C33" s="2" t="s">
@@ -3211,28 +3221,28 @@
       <c r="D33" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E33" s="9">
         <f t="shared" si="19"/>
         <v>3885</v>
       </c>
-      <c r="F33" s="10">
+      <c r="F33" s="9">
         <f t="shared" si="20"/>
         <v>4725</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="9">
         <f t="shared" si="21"/>
         <v>5670</v>
       </c>
-      <c r="H33" s="10">
+      <c r="H33" s="9">
         <f t="shared" si="22"/>
         <v>8925</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="12">
         <v>2026</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -3241,28 +3251,28 @@
       <c r="D34" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E34" s="10">
+      <c r="E34" s="9">
         <f t="shared" si="19"/>
         <v>3885</v>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="9">
         <f t="shared" si="20"/>
         <v>4725</v>
       </c>
-      <c r="G34" s="10">
+      <c r="G34" s="9">
         <f t="shared" si="21"/>
         <v>5670</v>
       </c>
-      <c r="H34" s="10">
+      <c r="H34" s="9">
         <f t="shared" si="22"/>
         <v>8925</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B35" s="13">
+      <c r="B35" s="12">
         <v>2026</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -3271,28 +3281,28 @@
       <c r="D35" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E35" s="10">
+      <c r="E35" s="9">
         <f t="shared" si="19"/>
         <v>3885</v>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="9">
         <f t="shared" si="20"/>
         <v>4725</v>
       </c>
-      <c r="G35" s="10">
+      <c r="G35" s="9">
         <f t="shared" si="21"/>
         <v>5670</v>
       </c>
-      <c r="H35" s="10">
+      <c r="H35" s="9">
         <f t="shared" si="22"/>
         <v>8925</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="12">
         <v>2026</v>
       </c>
       <c r="C36" s="2" t="s">
@@ -3301,28 +3311,28 @@
       <c r="D36" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E36" s="10">
+      <c r="E36" s="9">
         <f t="shared" si="19"/>
         <v>3885</v>
       </c>
-      <c r="F36" s="10">
+      <c r="F36" s="9">
         <f t="shared" si="20"/>
         <v>4725</v>
       </c>
-      <c r="G36" s="10">
+      <c r="G36" s="9">
         <f t="shared" si="21"/>
         <v>5670</v>
       </c>
-      <c r="H36" s="10">
+      <c r="H36" s="9">
         <f t="shared" si="22"/>
         <v>8925</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="12">
         <v>2026</v>
       </c>
       <c r="C37" s="2" t="s">
@@ -3331,28 +3341,28 @@
       <c r="D37" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E37" s="10">
+      <c r="E37" s="9">
         <f t="shared" si="19"/>
         <v>3885</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F37" s="9">
         <f t="shared" si="20"/>
         <v>4725</v>
       </c>
-      <c r="G37" s="10">
+      <c r="G37" s="9">
         <f t="shared" si="21"/>
         <v>5670</v>
       </c>
-      <c r="H37" s="10">
+      <c r="H37" s="9">
         <f t="shared" si="22"/>
         <v>8925</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B38" s="13">
+      <c r="B38" s="12">
         <v>2026</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -3361,28 +3371,28 @@
       <c r="D38" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E38" s="10">
+      <c r="E38" s="9">
         <f t="shared" si="19"/>
         <v>3885</v>
       </c>
-      <c r="F38" s="10">
+      <c r="F38" s="9">
         <f t="shared" si="20"/>
         <v>4725</v>
       </c>
-      <c r="G38" s="10">
+      <c r="G38" s="9">
         <f t="shared" si="21"/>
         <v>5670</v>
       </c>
-      <c r="H38" s="10">
+      <c r="H38" s="9">
         <f t="shared" si="22"/>
         <v>8925</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B39" s="13">
+      <c r="B39" s="12">
         <v>2026</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -3391,28 +3401,28 @@
       <c r="D39" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E39" s="10">
+      <c r="E39" s="9">
         <f>5000*1.05</f>
         <v>5250</v>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="9">
         <f>6000*1.05</f>
         <v>6300</v>
       </c>
-      <c r="G39" s="10">
+      <c r="G39" s="9">
         <f>6600*1.05</f>
         <v>6930</v>
       </c>
-      <c r="H39" s="10">
+      <c r="H39" s="9">
         <f>10800*1.05</f>
         <v>11340</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B40" s="13">
+      <c r="B40" s="12">
         <v>2026</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -3421,28 +3431,28 @@
       <c r="D40" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E40" s="10">
+      <c r="E40" s="9">
         <f t="shared" ref="E40:E44" si="23">5000*1.05</f>
         <v>5250</v>
       </c>
-      <c r="F40" s="10">
+      <c r="F40" s="9">
         <f t="shared" ref="F40:F44" si="24">6000*1.05</f>
         <v>6300</v>
       </c>
-      <c r="G40" s="10">
+      <c r="G40" s="9">
         <f t="shared" ref="G40:G44" si="25">6600*1.05</f>
         <v>6930</v>
       </c>
-      <c r="H40" s="10">
+      <c r="H40" s="9">
         <f t="shared" ref="H40:H44" si="26">10800*1.05</f>
         <v>11340</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B41" s="13">
+      <c r="B41" s="12">
         <v>2026</v>
       </c>
       <c r="C41" s="2" t="s">
@@ -3451,28 +3461,28 @@
       <c r="D41" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E41" s="10">
+      <c r="E41" s="9">
         <f t="shared" si="23"/>
         <v>5250</v>
       </c>
-      <c r="F41" s="10">
+      <c r="F41" s="9">
         <f t="shared" si="24"/>
         <v>6300</v>
       </c>
-      <c r="G41" s="10">
+      <c r="G41" s="9">
         <f t="shared" si="25"/>
         <v>6930</v>
       </c>
-      <c r="H41" s="10">
+      <c r="H41" s="9">
         <f t="shared" si="26"/>
         <v>11340</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B42" s="13">
+      <c r="B42" s="12">
         <v>2026</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -3481,28 +3491,28 @@
       <c r="D42" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E42" s="10">
+      <c r="E42" s="9">
         <f t="shared" si="23"/>
         <v>5250</v>
       </c>
-      <c r="F42" s="10">
+      <c r="F42" s="9">
         <f t="shared" si="24"/>
         <v>6300</v>
       </c>
-      <c r="G42" s="10">
+      <c r="G42" s="9">
         <f t="shared" si="25"/>
         <v>6930</v>
       </c>
-      <c r="H42" s="10">
+      <c r="H42" s="9">
         <f t="shared" si="26"/>
         <v>11340</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B43" s="13">
+      <c r="B43" s="12">
         <v>2026</v>
       </c>
       <c r="C43" s="2" t="s">
@@ -3511,28 +3521,28 @@
       <c r="D43" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E43" s="10">
+      <c r="E43" s="9">
         <f t="shared" si="23"/>
         <v>5250</v>
       </c>
-      <c r="F43" s="10">
+      <c r="F43" s="9">
         <f t="shared" si="24"/>
         <v>6300</v>
       </c>
-      <c r="G43" s="10">
+      <c r="G43" s="9">
         <f t="shared" si="25"/>
         <v>6930</v>
       </c>
-      <c r="H43" s="10">
+      <c r="H43" s="9">
         <f t="shared" si="26"/>
         <v>11340</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B44" s="13">
+      <c r="B44" s="12">
         <v>2026</v>
       </c>
       <c r="C44" s="2" t="s">
@@ -3541,28 +3551,28 @@
       <c r="D44" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E44" s="10">
+      <c r="E44" s="9">
         <f t="shared" si="23"/>
         <v>5250</v>
       </c>
-      <c r="F44" s="10">
+      <c r="F44" s="9">
         <f t="shared" si="24"/>
         <v>6300</v>
       </c>
-      <c r="G44" s="10">
+      <c r="G44" s="9">
         <f t="shared" si="25"/>
         <v>6930</v>
       </c>
-      <c r="H44" s="10">
+      <c r="H44" s="9">
         <f t="shared" si="26"/>
         <v>11340</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B45" s="13">
+      <c r="B45" s="12">
         <v>2026</v>
       </c>
       <c r="C45" s="2" t="s">
@@ -3571,28 +3581,28 @@
       <c r="D45" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E45" s="10">
+      <c r="E45" s="9">
         <f>4900*1.05</f>
         <v>5145</v>
       </c>
-      <c r="F45" s="10">
+      <c r="F45" s="9">
         <f>5200*1.05</f>
         <v>5460</v>
       </c>
-      <c r="G45" s="10">
+      <c r="G45" s="9">
         <f>5900*1.05</f>
         <v>6195</v>
       </c>
-      <c r="H45" s="10">
+      <c r="H45" s="9">
         <f>9300*1.05</f>
         <v>9765</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B46" s="13">
+      <c r="B46" s="12">
         <v>2026</v>
       </c>
       <c r="C46" s="2" t="s">
@@ -3601,28 +3611,28 @@
       <c r="D46" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E46" s="10">
+      <c r="E46" s="9">
         <f t="shared" ref="E46:E51" si="27">4900*1.05</f>
         <v>5145</v>
       </c>
-      <c r="F46" s="10">
+      <c r="F46" s="9">
         <f t="shared" ref="F46:F51" si="28">5200*1.05</f>
         <v>5460</v>
       </c>
-      <c r="G46" s="10">
+      <c r="G46" s="9">
         <f t="shared" ref="G46:G51" si="29">5900*1.05</f>
         <v>6195</v>
       </c>
-      <c r="H46" s="10">
+      <c r="H46" s="9">
         <f t="shared" ref="H46:H51" si="30">9300*1.05</f>
         <v>9765</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B47" s="13">
+      <c r="B47" s="12">
         <v>2026</v>
       </c>
       <c r="C47" s="2" t="s">
@@ -3631,28 +3641,28 @@
       <c r="D47" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E47" s="10">
+      <c r="E47" s="9">
         <f t="shared" si="27"/>
         <v>5145</v>
       </c>
-      <c r="F47" s="10">
+      <c r="F47" s="9">
         <f t="shared" si="28"/>
         <v>5460</v>
       </c>
-      <c r="G47" s="10">
+      <c r="G47" s="9">
         <f t="shared" si="29"/>
         <v>6195</v>
       </c>
-      <c r="H47" s="10">
+      <c r="H47" s="9">
         <f t="shared" si="30"/>
         <v>9765</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B48" s="13">
+      <c r="B48" s="12">
         <v>2026</v>
       </c>
       <c r="C48" s="2" t="s">
@@ -3661,28 +3671,28 @@
       <c r="D48" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E48" s="10">
+      <c r="E48" s="9">
         <f t="shared" si="27"/>
         <v>5145</v>
       </c>
-      <c r="F48" s="10">
+      <c r="F48" s="9">
         <f t="shared" si="28"/>
         <v>5460</v>
       </c>
-      <c r="G48" s="10">
+      <c r="G48" s="9">
         <f t="shared" si="29"/>
         <v>6195</v>
       </c>
-      <c r="H48" s="10">
+      <c r="H48" s="9">
         <f t="shared" si="30"/>
         <v>9765</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B49" s="13">
+      <c r="B49" s="12">
         <v>2026</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -3691,28 +3701,28 @@
       <c r="D49" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E49" s="10">
+      <c r="E49" s="9">
         <f t="shared" si="27"/>
         <v>5145</v>
       </c>
-      <c r="F49" s="10">
+      <c r="F49" s="9">
         <f t="shared" si="28"/>
         <v>5460</v>
       </c>
-      <c r="G49" s="10">
+      <c r="G49" s="9">
         <f t="shared" si="29"/>
         <v>6195</v>
       </c>
-      <c r="H49" s="10">
+      <c r="H49" s="9">
         <f t="shared" si="30"/>
         <v>9765</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B50" s="13">
+      <c r="B50" s="12">
         <v>2026</v>
       </c>
       <c r="C50" s="2" t="s">
@@ -3721,28 +3731,28 @@
       <c r="D50" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E50" s="10">
+      <c r="E50" s="9">
         <f t="shared" si="27"/>
         <v>5145</v>
       </c>
-      <c r="F50" s="10">
+      <c r="F50" s="9">
         <f t="shared" si="28"/>
         <v>5460</v>
       </c>
-      <c r="G50" s="10">
+      <c r="G50" s="9">
         <f t="shared" si="29"/>
         <v>6195</v>
       </c>
-      <c r="H50" s="10">
+      <c r="H50" s="9">
         <f t="shared" si="30"/>
         <v>9765</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B51" s="13">
+      <c r="B51" s="12">
         <v>2026</v>
       </c>
       <c r="C51" s="2" t="s">
@@ -3751,28 +3761,28 @@
       <c r="D51" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E51" s="10">
+      <c r="E51" s="9">
         <f t="shared" si="27"/>
         <v>5145</v>
       </c>
-      <c r="F51" s="10">
+      <c r="F51" s="9">
         <f t="shared" si="28"/>
         <v>5460</v>
       </c>
-      <c r="G51" s="10">
+      <c r="G51" s="9">
         <f t="shared" si="29"/>
         <v>6195</v>
       </c>
-      <c r="H51" s="10">
+      <c r="H51" s="9">
         <f t="shared" si="30"/>
         <v>9765</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B52" s="13">
+      <c r="B52" s="12">
         <v>2026</v>
       </c>
       <c r="C52" s="2" t="s">
@@ -3781,26 +3791,26 @@
       <c r="D52" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E52" s="10">
+      <c r="E52" s="9">
         <v>5250</v>
       </c>
-      <c r="F52" s="10">
+      <c r="F52" s="9">
         <v>6300</v>
       </c>
-      <c r="G52" s="10">
+      <c r="G52" s="9">
         <f>6700*1.05</f>
         <v>7035</v>
       </c>
-      <c r="H52" s="10">
+      <c r="H52" s="9">
         <f>11000*1.05</f>
         <v>11550</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B53" s="13">
+      <c r="B53" s="12">
         <v>2026</v>
       </c>
       <c r="C53" s="2" t="s">
@@ -3809,26 +3819,26 @@
       <c r="D53" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E53" s="10">
+      <c r="E53" s="9">
         <v>5250</v>
       </c>
-      <c r="F53" s="10">
+      <c r="F53" s="9">
         <v>6300</v>
       </c>
-      <c r="G53" s="10">
+      <c r="G53" s="9">
         <f t="shared" ref="G53:G65" si="31">6700*1.05</f>
         <v>7035</v>
       </c>
-      <c r="H53" s="10">
+      <c r="H53" s="9">
         <f t="shared" ref="H53:H65" si="32">11000*1.05</f>
         <v>11550</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B54" s="13">
+      <c r="B54" s="12">
         <v>2026</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -3837,26 +3847,26 @@
       <c r="D54" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E54" s="10">
+      <c r="E54" s="9">
         <v>5250</v>
       </c>
-      <c r="F54" s="10">
+      <c r="F54" s="9">
         <v>6300</v>
       </c>
-      <c r="G54" s="10">
+      <c r="G54" s="9">
         <f t="shared" si="31"/>
         <v>7035</v>
       </c>
-      <c r="H54" s="10">
+      <c r="H54" s="9">
         <f t="shared" si="32"/>
         <v>11550</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B55" s="13">
+      <c r="B55" s="12">
         <v>2026</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -3865,26 +3875,26 @@
       <c r="D55" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E55" s="10">
+      <c r="E55" s="9">
         <v>5250</v>
       </c>
-      <c r="F55" s="10">
+      <c r="F55" s="9">
         <v>6300</v>
       </c>
-      <c r="G55" s="10">
+      <c r="G55" s="9">
         <f t="shared" si="31"/>
         <v>7035</v>
       </c>
-      <c r="H55" s="10">
+      <c r="H55" s="9">
         <f t="shared" si="32"/>
         <v>11550</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B56" s="13">
+      <c r="B56" s="12">
         <v>2026</v>
       </c>
       <c r="C56" s="2" t="s">
@@ -3893,26 +3903,26 @@
       <c r="D56" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E56" s="10">
+      <c r="E56" s="9">
         <v>5250</v>
       </c>
-      <c r="F56" s="10">
+      <c r="F56" s="9">
         <v>6300</v>
       </c>
-      <c r="G56" s="10">
+      <c r="G56" s="9">
         <f t="shared" si="31"/>
         <v>7035</v>
       </c>
-      <c r="H56" s="10">
+      <c r="H56" s="9">
         <f t="shared" si="32"/>
         <v>11550</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B57" s="13">
+      <c r="B57" s="12">
         <v>2026</v>
       </c>
       <c r="C57" s="2" t="s">
@@ -3921,26 +3931,26 @@
       <c r="D57" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E57" s="10">
+      <c r="E57" s="9">
         <v>5250</v>
       </c>
-      <c r="F57" s="10">
+      <c r="F57" s="9">
         <v>6300</v>
       </c>
-      <c r="G57" s="10">
+      <c r="G57" s="9">
         <f t="shared" si="31"/>
         <v>7035</v>
       </c>
-      <c r="H57" s="10">
+      <c r="H57" s="9">
         <f t="shared" si="32"/>
         <v>11550</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B58" s="13">
+      <c r="B58" s="12">
         <v>2026</v>
       </c>
       <c r="C58" s="2" t="s">
@@ -3949,26 +3959,26 @@
       <c r="D58" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E58" s="10">
+      <c r="E58" s="9">
         <v>5250</v>
       </c>
-      <c r="F58" s="10">
+      <c r="F58" s="9">
         <v>6300</v>
       </c>
-      <c r="G58" s="10">
+      <c r="G58" s="9">
         <f t="shared" si="31"/>
         <v>7035</v>
       </c>
-      <c r="H58" s="10">
+      <c r="H58" s="9">
         <f t="shared" si="32"/>
         <v>11550</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B59" s="13">
+      <c r="B59" s="12">
         <v>2026</v>
       </c>
       <c r="C59" s="2" t="s">
@@ -3977,26 +3987,26 @@
       <c r="D59" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E59" s="10">
+      <c r="E59" s="9">
         <v>5250</v>
       </c>
-      <c r="F59" s="10">
+      <c r="F59" s="9">
         <v>6300</v>
       </c>
-      <c r="G59" s="10">
+      <c r="G59" s="9">
         <f t="shared" si="31"/>
         <v>7035</v>
       </c>
-      <c r="H59" s="10">
+      <c r="H59" s="9">
         <f t="shared" si="32"/>
         <v>11550</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B60" s="13">
+      <c r="B60" s="12">
         <v>2026</v>
       </c>
       <c r="C60" s="2" t="s">
@@ -4005,26 +4015,26 @@
       <c r="D60" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E60" s="10">
+      <c r="E60" s="9">
         <v>5250</v>
       </c>
-      <c r="F60" s="10">
+      <c r="F60" s="9">
         <v>6300</v>
       </c>
-      <c r="G60" s="10">
+      <c r="G60" s="9">
         <f t="shared" si="31"/>
         <v>7035</v>
       </c>
-      <c r="H60" s="10">
+      <c r="H60" s="9">
         <f t="shared" si="32"/>
         <v>11550</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B61" s="13">
+      <c r="B61" s="12">
         <v>2026</v>
       </c>
       <c r="C61" s="2" t="s">
@@ -4033,26 +4043,26 @@
       <c r="D61" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E61" s="10">
+      <c r="E61" s="9">
         <v>5250</v>
       </c>
-      <c r="F61" s="10">
+      <c r="F61" s="9">
         <v>6300</v>
       </c>
-      <c r="G61" s="10">
+      <c r="G61" s="9">
         <f t="shared" si="31"/>
         <v>7035</v>
       </c>
-      <c r="H61" s="10">
+      <c r="H61" s="9">
         <f t="shared" si="32"/>
         <v>11550</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B62" s="13">
+      <c r="B62" s="12">
         <v>2026</v>
       </c>
       <c r="C62" s="2" t="s">
@@ -4061,26 +4071,26 @@
       <c r="D62" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="E62" s="10">
+      <c r="E62" s="9">
         <v>5250</v>
       </c>
-      <c r="F62" s="10">
+      <c r="F62" s="9">
         <v>6300</v>
       </c>
-      <c r="G62" s="10">
+      <c r="G62" s="9">
         <f t="shared" si="31"/>
         <v>7035</v>
       </c>
-      <c r="H62" s="10">
+      <c r="H62" s="9">
         <f t="shared" si="32"/>
         <v>11550</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B63" s="13">
+      <c r="B63" s="12">
         <v>2026</v>
       </c>
       <c r="C63" s="2" t="s">
@@ -4089,26 +4099,26 @@
       <c r="D63" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E63" s="10">
+      <c r="E63" s="9">
         <v>5250</v>
       </c>
-      <c r="F63" s="10">
+      <c r="F63" s="9">
         <v>6300</v>
       </c>
-      <c r="G63" s="10">
+      <c r="G63" s="9">
         <f t="shared" si="31"/>
         <v>7035</v>
       </c>
-      <c r="H63" s="10">
+      <c r="H63" s="9">
         <f t="shared" si="32"/>
         <v>11550</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B64" s="13">
+      <c r="B64" s="12">
         <v>2026</v>
       </c>
       <c r="C64" s="2" t="s">
@@ -4117,26 +4127,26 @@
       <c r="D64" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E64" s="10">
+      <c r="E64" s="9">
         <v>5250</v>
       </c>
-      <c r="F64" s="10">
+      <c r="F64" s="9">
         <v>6300</v>
       </c>
-      <c r="G64" s="10">
+      <c r="G64" s="9">
         <f t="shared" si="31"/>
         <v>7035</v>
       </c>
-      <c r="H64" s="10">
+      <c r="H64" s="9">
         <f t="shared" si="32"/>
         <v>11550</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B65" s="13">
+      <c r="B65" s="12">
         <v>2026</v>
       </c>
       <c r="C65" s="2" t="s">
@@ -4145,26 +4155,26 @@
       <c r="D65" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E65" s="10">
+      <c r="E65" s="9">
         <v>5250</v>
       </c>
-      <c r="F65" s="10">
+      <c r="F65" s="9">
         <v>6300</v>
       </c>
-      <c r="G65" s="10">
+      <c r="G65" s="9">
         <f t="shared" si="31"/>
         <v>7035</v>
       </c>
-      <c r="H65" s="10">
+      <c r="H65" s="9">
         <f t="shared" si="32"/>
         <v>11550</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B66" s="13">
+      <c r="B66" s="12">
         <v>2026</v>
       </c>
       <c r="C66" s="2" t="s">
@@ -4173,28 +4183,28 @@
       <c r="D66" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E66" s="10">
+      <c r="E66" s="9">
         <f>4500*1.05</f>
         <v>4725</v>
       </c>
-      <c r="F66" s="10">
+      <c r="F66" s="9">
         <f>5400*1.05</f>
         <v>5670</v>
       </c>
-      <c r="G66" s="10">
+      <c r="G66" s="9">
         <f>6100*1.05</f>
         <v>6405</v>
       </c>
-      <c r="H66" s="10">
+      <c r="H66" s="9">
         <f>9700*1.05</f>
         <v>10185</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B67" s="13">
+      <c r="B67" s="12">
         <v>2026</v>
       </c>
       <c r="C67" s="2" t="s">
@@ -4203,28 +4213,28 @@
       <c r="D67" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E67" s="10">
+      <c r="E67" s="9">
         <f t="shared" ref="E67:E70" si="33">4500*1.05</f>
         <v>4725</v>
       </c>
-      <c r="F67" s="10">
+      <c r="F67" s="9">
         <f t="shared" ref="F67:F70" si="34">5400*1.05</f>
         <v>5670</v>
       </c>
-      <c r="G67" s="10">
+      <c r="G67" s="9">
         <f t="shared" ref="G67:G70" si="35">6100*1.05</f>
         <v>6405</v>
       </c>
-      <c r="H67" s="10">
+      <c r="H67" s="9">
         <f t="shared" ref="H67:H70" si="36">9700*1.05</f>
         <v>10185</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B68" s="13">
+      <c r="B68" s="12">
         <v>2026</v>
       </c>
       <c r="C68" s="2" t="s">
@@ -4233,28 +4243,28 @@
       <c r="D68" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E68" s="10">
+      <c r="E68" s="9">
         <f t="shared" si="33"/>
         <v>4725</v>
       </c>
-      <c r="F68" s="10">
+      <c r="F68" s="9">
         <f t="shared" si="34"/>
         <v>5670</v>
       </c>
-      <c r="G68" s="10">
+      <c r="G68" s="9">
         <f t="shared" si="35"/>
         <v>6405</v>
       </c>
-      <c r="H68" s="10">
+      <c r="H68" s="9">
         <f t="shared" si="36"/>
         <v>10185</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B69" s="13">
+      <c r="B69" s="12">
         <v>2026</v>
       </c>
       <c r="C69" s="2" t="s">
@@ -4263,28 +4273,28 @@
       <c r="D69" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E69" s="10">
+      <c r="E69" s="9">
         <f t="shared" si="33"/>
         <v>4725</v>
       </c>
-      <c r="F69" s="10">
+      <c r="F69" s="9">
         <f t="shared" si="34"/>
         <v>5670</v>
       </c>
-      <c r="G69" s="10">
+      <c r="G69" s="9">
         <f t="shared" si="35"/>
         <v>6405</v>
       </c>
-      <c r="H69" s="10">
+      <c r="H69" s="9">
         <f t="shared" si="36"/>
         <v>10185</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B70" s="13">
+      <c r="B70" s="12">
         <v>2026</v>
       </c>
       <c r="C70" s="2" t="s">
@@ -4293,28 +4303,28 @@
       <c r="D70" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E70" s="10">
+      <c r="E70" s="9">
         <f t="shared" si="33"/>
         <v>4725</v>
       </c>
-      <c r="F70" s="10">
+      <c r="F70" s="9">
         <f t="shared" si="34"/>
         <v>5670</v>
       </c>
-      <c r="G70" s="10">
+      <c r="G70" s="9">
         <f t="shared" si="35"/>
         <v>6405</v>
       </c>
-      <c r="H70" s="10">
+      <c r="H70" s="9">
         <f t="shared" si="36"/>
         <v>10185</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B71" s="13">
+      <c r="B71" s="12">
         <v>2026</v>
       </c>
       <c r="C71" s="2" t="s">
@@ -4323,28 +4333,28 @@
       <c r="D71" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E71" s="10">
+      <c r="E71" s="9">
         <f>4900*1.05</f>
         <v>5145</v>
       </c>
-      <c r="F71" s="10">
+      <c r="F71" s="9">
         <f>5700*1.05</f>
         <v>5985</v>
       </c>
-      <c r="G71" s="10">
+      <c r="G71" s="9">
         <f>6400*1.05</f>
         <v>6720</v>
       </c>
-      <c r="H71" s="10">
+      <c r="H71" s="9">
         <f>10400*1.05</f>
         <v>10920</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B72" s="13">
+      <c r="B72" s="12">
         <v>2026</v>
       </c>
       <c r="C72" s="2" t="s">
@@ -4353,28 +4363,28 @@
       <c r="D72" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E72" s="10">
+      <c r="E72" s="9">
         <f t="shared" ref="E72:E80" si="37">4900*1.05</f>
         <v>5145</v>
       </c>
-      <c r="F72" s="10">
+      <c r="F72" s="9">
         <f t="shared" ref="F72:F74" si="38">5700*1.05</f>
         <v>5985</v>
       </c>
-      <c r="G72" s="10">
+      <c r="G72" s="9">
         <f t="shared" ref="G72:G74" si="39">6400*1.05</f>
         <v>6720</v>
       </c>
-      <c r="H72" s="10">
+      <c r="H72" s="9">
         <f t="shared" ref="H72:H74" si="40">10400*1.05</f>
         <v>10920</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B73" s="13">
+      <c r="B73" s="12">
         <v>2026</v>
       </c>
       <c r="C73" s="2" t="s">
@@ -4383,28 +4393,28 @@
       <c r="D73" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E73" s="10">
+      <c r="E73" s="9">
         <f t="shared" si="37"/>
         <v>5145</v>
       </c>
-      <c r="F73" s="10">
+      <c r="F73" s="9">
         <f t="shared" si="38"/>
         <v>5985</v>
       </c>
-      <c r="G73" s="10">
+      <c r="G73" s="9">
         <f t="shared" si="39"/>
         <v>6720</v>
       </c>
-      <c r="H73" s="10">
+      <c r="H73" s="9">
         <f t="shared" si="40"/>
         <v>10920</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B74" s="13">
+      <c r="B74" s="12">
         <v>2026</v>
       </c>
       <c r="C74" s="2" t="s">
@@ -4413,28 +4423,28 @@
       <c r="D74" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E74" s="10">
+      <c r="E74" s="9">
         <f t="shared" si="37"/>
         <v>5145</v>
       </c>
-      <c r="F74" s="10">
+      <c r="F74" s="9">
         <f t="shared" si="38"/>
         <v>5985</v>
       </c>
-      <c r="G74" s="10">
+      <c r="G74" s="9">
         <f t="shared" si="39"/>
         <v>6720</v>
       </c>
-      <c r="H74" s="10">
+      <c r="H74" s="9">
         <f t="shared" si="40"/>
         <v>10920</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B75" s="13">
+      <c r="B75" s="12">
         <v>2026</v>
       </c>
       <c r="C75" s="2" t="s">
@@ -4443,28 +4453,28 @@
       <c r="D75" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E75" s="10">
+      <c r="E75" s="9">
         <f t="shared" si="37"/>
         <v>5145</v>
       </c>
-      <c r="F75" s="10">
+      <c r="F75" s="9">
         <f>5900*1.05</f>
         <v>6195</v>
       </c>
-      <c r="G75" s="10">
+      <c r="G75" s="9">
         <f>6600*1.05</f>
         <v>6930</v>
       </c>
-      <c r="H75" s="10">
+      <c r="H75" s="9">
         <f>10700*1.05</f>
         <v>11235</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B76" s="13">
+      <c r="B76" s="12">
         <v>2026</v>
       </c>
       <c r="C76" s="2" t="s">
@@ -4473,28 +4483,28 @@
       <c r="D76" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E76" s="10">
+      <c r="E76" s="9">
         <f t="shared" si="37"/>
         <v>5145</v>
       </c>
-      <c r="F76" s="10">
+      <c r="F76" s="9">
         <f t="shared" ref="F76:F80" si="41">5900*1.05</f>
         <v>6195</v>
       </c>
-      <c r="G76" s="10">
+      <c r="G76" s="9">
         <f t="shared" ref="G76:G80" si="42">6600*1.05</f>
         <v>6930</v>
       </c>
-      <c r="H76" s="10">
+      <c r="H76" s="9">
         <f t="shared" ref="H76:H80" si="43">10700*1.05</f>
         <v>11235</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B77" s="13">
+      <c r="B77" s="12">
         <v>2026</v>
       </c>
       <c r="C77" s="2" t="s">
@@ -4503,28 +4513,28 @@
       <c r="D77" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E77" s="10">
+      <c r="E77" s="9">
         <f t="shared" si="37"/>
         <v>5145</v>
       </c>
-      <c r="F77" s="10">
+      <c r="F77" s="9">
         <f t="shared" si="41"/>
         <v>6195</v>
       </c>
-      <c r="G77" s="10">
+      <c r="G77" s="9">
         <f t="shared" si="42"/>
         <v>6930</v>
       </c>
-      <c r="H77" s="10">
+      <c r="H77" s="9">
         <f t="shared" si="43"/>
         <v>11235</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B78" s="13">
+      <c r="B78" s="12">
         <v>2026</v>
       </c>
       <c r="C78" s="2" t="s">
@@ -4533,28 +4543,28 @@
       <c r="D78" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E78" s="10">
+      <c r="E78" s="9">
         <f t="shared" si="37"/>
         <v>5145</v>
       </c>
-      <c r="F78" s="10">
+      <c r="F78" s="9">
         <f t="shared" si="41"/>
         <v>6195</v>
       </c>
-      <c r="G78" s="10">
+      <c r="G78" s="9">
         <f t="shared" si="42"/>
         <v>6930</v>
       </c>
-      <c r="H78" s="10">
+      <c r="H78" s="9">
         <f t="shared" si="43"/>
         <v>11235</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B79" s="13">
+      <c r="B79" s="12">
         <v>2026</v>
       </c>
       <c r="C79" s="2" t="s">
@@ -4563,28 +4573,28 @@
       <c r="D79" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E79" s="10">
+      <c r="E79" s="9">
         <f t="shared" si="37"/>
         <v>5145</v>
       </c>
-      <c r="F79" s="10">
+      <c r="F79" s="9">
         <f t="shared" si="41"/>
         <v>6195</v>
       </c>
-      <c r="G79" s="10">
+      <c r="G79" s="9">
         <f t="shared" si="42"/>
         <v>6930</v>
       </c>
-      <c r="H79" s="10">
+      <c r="H79" s="9">
         <f t="shared" si="43"/>
         <v>11235</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B80" s="13">
+      <c r="B80" s="12">
         <v>2026</v>
       </c>
       <c r="C80" s="2" t="s">
@@ -4593,943 +4603,943 @@
       <c r="D80" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E80" s="10">
+      <c r="E80" s="9">
         <f t="shared" si="37"/>
         <v>5145</v>
       </c>
-      <c r="F80" s="10">
+      <c r="F80" s="9">
         <f t="shared" si="41"/>
         <v>6195</v>
       </c>
-      <c r="G80" s="10">
+      <c r="G80" s="9">
         <f t="shared" si="42"/>
         <v>6930</v>
       </c>
-      <c r="H80" s="10">
+      <c r="H80" s="9">
         <f t="shared" si="43"/>
         <v>11235</v>
       </c>
     </row>
-    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="241" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="242" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="243" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="244" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="245" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="246" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="247" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="248" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="249" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="250" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="251" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="252" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="253" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="254" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="255" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="256" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="257" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="258" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="259" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="260" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="261" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="262" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="263" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="264" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="266" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="267" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="268" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="269" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="270" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="271" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="272" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="273" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="274" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="275" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="276" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="277" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="278" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="279" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="280" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="281" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="282" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="283" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="284" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="285" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="286" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="287" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="288" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="324" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="325" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="326" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="327" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="328" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="329" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="330" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="331" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="332" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="333" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="334" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="335" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="336" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="337" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="338" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="339" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="340" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="341" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="342" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="343" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="344" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="345" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="346" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="347" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="348" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="349" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="350" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="351" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="352" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="353" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="354" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="355" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="356" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="357" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="358" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="359" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="360" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="361" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="362" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="363" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="364" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="365" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="366" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="367" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="368" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="369" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="370" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="371" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="372" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="373" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="374" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="375" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="376" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="377" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="378" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="379" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="380" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="381" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="382" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="383" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="384" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
